--- a/data/trans_orig/IP1008-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117434</t>
+          <t>118049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223940</t>
+          <t>223515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249956</t>
+          <t>249355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249158</t>
+          <t>249651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501542</t>
+          <t>501298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124485</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137408</t>
+          <t>136763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263945</t>
+          <t>263882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>268539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>187964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193445</t>
+          <t>193444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202636</t>
+          <t>202630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393434</t>
+          <t>393420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399468</t>
+          <t>399462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,77 +2124,77 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9021</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12893</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12663</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673350</t>
+          <t>673656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>679837</t>
+          <t>679838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,82 +2232,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>714502</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>721322</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>713679</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720682</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1396400</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1390828</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1399729</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,72%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1396400</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1391058</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1399961</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>142470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141104</t>
+          <t>141124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285967</t>
+          <t>286408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229065</t>
+          <t>229361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496573</t>
+          <t>496221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149953</t>
+          <t>150128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308388</t>
+          <t>308611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171727</t>
+          <t>171606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177310</t>
+          <t>177304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>342830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348644</t>
+          <t>348609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699019</t>
+          <t>698695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>705573</t>
+          <t>705570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740819</t>
+          <t>740983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746861</t>
+          <t>746886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442876</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451733</t>
+          <t>1451702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205690</t>
+          <t>206311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464398</t>
+          <t>463101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182095</t>
+          <t>182686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188283</t>
+          <t>188287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370597</t>
+          <t>371141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166824</t>
+          <t>167449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172675</t>
+          <t>172654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168689</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338223</t>
+          <t>338572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345323</t>
+          <t>345440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>692806</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>701524</t>
+          <t>701545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739767</t>
+          <t>739423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744260</t>
+          <t>744257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1435300</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1444527</t>
+          <t>1445006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1008-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4036</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117880</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120675</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118049</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>343</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223515</t>
+          <t>223612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4098</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252398</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249658</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252563</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>249355</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>250205</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252398</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>249651</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>758</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501298</t>
+          <t>500979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506321</t>
+          <t>506320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>527</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140157</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127021</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>124312</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>124906</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140157</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136763</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>400</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263882</t>
+          <t>264134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268539</t>
+          <t>268536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2052</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3419</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205369</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>192045</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>187964</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>193444</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>188589</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>193447</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205369</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202630</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>592</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393420</t>
+          <t>393880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399462</t>
+          <t>399467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8886</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8198</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>713814</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721319</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>677801</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673656</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>679838</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>673241</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>679854</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714502</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721322</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390828</t>
+          <t>1390761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399729</t>
+          <t>1399822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,102 +2674,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3811</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2808</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3389</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141114</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>145654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>143473</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143839</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141124</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>421</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286408</t>
+          <t>286217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1480</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4565</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>232996</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>229361</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229293</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>706</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496221</t>
+          <t>497011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1390</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153444</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150128</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150452</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>446</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308611</t>
+          <t>308511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2593</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2593</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175364</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172069</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177307</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175364</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171606</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177304</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>501</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342830</t>
+          <t>342956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348609</t>
+          <t>348643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7240</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7159</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740902</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746860</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703430</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698695</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>705570</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698288</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>705568</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744875</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>740983</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746886</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1442893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451702</t>
+          <t>1451669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4206</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5145</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5477</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209142</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>206311</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>205728</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>710</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463101</t>
+          <t>463433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,74 +5302,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2313</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>186586</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>182686</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>188287</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>182684</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>188290</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>96,71%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>532</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371141</t>
+          <t>370962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2547</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6345</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172099</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168891</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173468</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170754</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167449</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>172654</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>166956</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>172674</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172099</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168680</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173463</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338572</t>
+          <t>338128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345440</t>
+          <t>345403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11751</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11767</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742895</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>739136</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744256</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>698136</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>692620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>701545</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>692604</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>701465</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742895</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739423</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744257</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1435614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1445006</t>
+          <t>1445038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
